--- a/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/日常报销单.xlsx
+++ b/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/日常报销单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aLJD\server\oa\dh-oa\dh-module-oa\dh-module-oa-server\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC624F20-CA3A-46BF-A36E-7CD3F0664EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A0C37B-47E9-4619-BDE6-F7B0D7607955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="3015" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>摘要</t>
   </si>
@@ -46,10 +46,6 @@
   </si>
   <si>
     <t>领款人签章</t>
-  </si>
-  <si>
-    <t>单位：{companyName}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>{year}年{month}月{day}日</t>
@@ -64,28 +60,36 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>{amountChinese}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>{totalAmount}</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>（{expenseType}）费 用 报 销 单</t>
+    <t>审批人</t>
+  </si>
+  <si>
+    <t>审核</t>
+  </si>
+  <si>
+    <t xml:space="preserve">证明或验收 </t>
+  </si>
+  <si>
+    <t>经手</t>
+  </si>
+  <si>
+    <t>人民币（大写）{amountChinese}</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>审批人</t>
-  </si>
-  <si>
-    <t>审核</t>
-  </si>
-  <si>
-    <t xml:space="preserve">证明或验收 </t>
-  </si>
-  <si>
-    <t>经手</t>
+    <t>（/）费 用 报 销 单</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：/</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{receiptCount}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -93,7 +97,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;#,##0"/>
+    <numFmt numFmtId="176" formatCode="&quot;¥&quot;#,##0.00;[Red]&quot;¥&quot;#,##0.00"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -107,12 +111,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="仿宋"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -120,23 +126,27 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="仿宋"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="仿宋"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -322,6 +332,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -358,17 +374,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -669,65 +679,65 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.875" customWidth="1"/>
-    <col min="2" max="2" width="17.5" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="31.125" customWidth="1"/>
+    <col min="2" max="2" width="22.75" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="26.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="A1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="72.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
+      <c r="B3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="13"/>
     </row>
     <row r="4" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="15"/>
+      <c r="B4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="17"/>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="13"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="6" t="s">
-        <v>10</v>
+      <c r="A5" s="15"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="72.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>1</v>
+      <c r="B6" s="21" t="s">
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -737,24 +747,24 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="20"/>
+      <c r="A7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="6"/>
     </row>
     <row r="8" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="20"/>
+      <c r="A8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/日常报销单.xlsx
+++ b/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/日常报销单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aLJD\server\oa\dh-oa\dh-module-oa\dh-module-oa-server\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A0C37B-47E9-4619-BDE6-F7B0D7607955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AE3A2A-6857-440D-A2F9-851257F7ABA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="3015" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -76,19 +76,31 @@
     <t>经手</t>
   </si>
   <si>
-    <t>人民币（大写）{amountChinese}</t>
+    <t>{receiptCount}</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>（/）费 用 报 销 单</t>
+    <t>费 用 报 销 单</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>单位：/</t>
+    <t>单位：中国引航协会</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>{receiptCount}</t>
+    <r>
+      <t>人民币（大写）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{amountChinese}</t>
+    </r>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -152,13 +164,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="仿宋"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color indexed="8"/>
       <name val="仿宋"/>
       <family val="3"/>
@@ -189,6 +194,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="仿宋"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="仿宋"/>
       <family val="3"/>
@@ -326,28 +339,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -362,23 +378,20 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -685,18 +698,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
     </row>
     <row r="2" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="21"/>
       <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
@@ -708,26 +721,26 @@
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="14"/>
     </row>
     <row r="4" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="17"/>
+      <c r="B4" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="18"/>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="15"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="19"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
@@ -736,8 +749,8 @@
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>16</v>
+      <c r="B6" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
